--- a/output/pdf_financials_xlsx/WBGD.xlsx
+++ b/output/pdf_financials_xlsx/WBGD.xlsx
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.234455</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.376805</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -3381,7 +3381,11 @@
           <t>Warrants reserve 5</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.234455</v>
       </c>

--- a/output/pdf_financials_xlsx/WBGD.xlsx
+++ b/output/pdf_financials_xlsx/WBGD.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.561174</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.434187</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003763</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.561174</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.434187</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003763</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.561593</v>
+        <v>0.000419</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.434606</v>
+        <v>0.000419</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004182</v>
+        <v>0.000419</v>
       </c>
     </row>
     <row r="49">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/WBGD.xlsx
+++ b/output/pdf_financials_xlsx/WBGD.xlsx
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.271974</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.552397</v>
       </c>
     </row>
     <row r="68">
@@ -3751,7 +3751,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>1.392205</v>
       </c>
